--- a/excel/50000(n)/RAW_Dataset.xlsx
+++ b/excel/50000(n)/RAW_Dataset.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\#Java-Practice\##SS2\Lab3 Sorting\excel\"/>
     </mc:Choice>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t xml:space="preserve">Algorithm </t>
   </si>
@@ -58,12 +58,91 @@
   </si>
   <si>
     <t>Trial 9</t>
+  </si>
+  <si>
+    <t>Bubble Sort</t>
+  </si>
+  <si>
+    <t>Bubble Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Insertion Sort</t>
+  </si>
+  <si>
+    <t>Insertion Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Selection Sort</t>
+  </si>
+  <si>
+    <t>Selection Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Merge Sort</t>
+  </si>
+  <si>
+    <t>Merge Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Quick Sort</t>
+  </si>
+  <si>
+    <t>Quick Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Trial 10</t>
+  </si>
+  <si>
+    <t>Trial 11</t>
+  </si>
+  <si>
+    <t>Trial 12</t>
+  </si>
+  <si>
+    <t>Trial 13</t>
+  </si>
+  <si>
+    <t>Trial 14</t>
+  </si>
+  <si>
+    <t>Trial 15</t>
+  </si>
+  <si>
+    <t>Trial 16</t>
+  </si>
+  <si>
+    <t>Trial 17</t>
+  </si>
+  <si>
+    <t>Trial 18</t>
+  </si>
+  <si>
+    <t>Trial 19</t>
+  </si>
+  <si>
+    <t>Trial 20</t>
+  </si>
+  <si>
+    <t>Trial 21</t>
+  </si>
+  <si>
+    <t>Trial 22</t>
+  </si>
+  <si>
+    <t>Trial 23</t>
+  </si>
+  <si>
+    <t>Trial 24</t>
+  </si>
+  <si>
+    <t>Trial 25</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -388,11 +467,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.77734375" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="14.77734375"/>
+    <col min="2" max="2" customWidth="true" width="13.33203125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.5">
@@ -402,32 +481,910 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" t="s" s="0">
         <v>10</v>
+      </c>
+      <c r="L1" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M1" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="P1" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="Q1" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="R1" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="S1" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="T1" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="U1" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="V1" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="W1" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="X1" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="Y1" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="Z1" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="AA1" t="s" s="0">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B2" t="n" s="0">
+        <v>50000.0</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.9297383E9</v>
+      </c>
+      <c r="D2" t="n" s="0">
+        <v>2.9295333E9</v>
+      </c>
+      <c r="E2" t="n" s="0">
+        <v>2.7136371E9</v>
+      </c>
+      <c r="F2" t="n" s="0">
+        <v>2.7123154E9</v>
+      </c>
+      <c r="G2" t="n" s="0">
+        <v>2.6907516E9</v>
+      </c>
+      <c r="H2" t="n" s="0">
+        <v>2.7008939E9</v>
+      </c>
+      <c r="I2" t="n" s="0">
+        <v>2.7009653E9</v>
+      </c>
+      <c r="J2" t="n" s="0">
+        <v>2.6894839E9</v>
+      </c>
+      <c r="K2" t="n" s="0">
+        <v>2.6580036E9</v>
+      </c>
+      <c r="L2" t="n" s="0">
+        <v>2.68731E9</v>
+      </c>
+      <c r="M2" t="n" s="0">
+        <v>2.6977844E9</v>
+      </c>
+      <c r="N2" t="n" s="0">
+        <v>2.6835422E9</v>
+      </c>
+      <c r="O2" t="n" s="0">
+        <v>2.6653594E9</v>
+      </c>
+      <c r="P2" t="n" s="0">
+        <v>2.6682922E9</v>
+      </c>
+      <c r="Q2" t="n" s="0">
+        <v>2.7419818E9</v>
+      </c>
+      <c r="R2" t="n" s="0">
+        <v>2.702526E9</v>
+      </c>
+      <c r="S2" t="n" s="0">
+        <v>2.677982E9</v>
+      </c>
+      <c r="T2" t="n" s="0">
+        <v>2.743893E9</v>
+      </c>
+      <c r="U2" t="n" s="0">
+        <v>2.8265783E9</v>
+      </c>
+      <c r="V2" t="n" s="0">
+        <v>2.6716759E9</v>
+      </c>
+      <c r="W2" t="n" s="0">
+        <v>2.6674882E9</v>
+      </c>
+      <c r="X2" t="n" s="0">
+        <v>2.6955672E9</v>
+      </c>
+      <c r="Y2" t="n" s="0">
+        <v>2.7034599E9</v>
+      </c>
+      <c r="Z2" t="n" s="0">
+        <v>2.6529342E9</v>
+      </c>
+      <c r="AA2" t="n" s="0">
+        <v>2.8159792E9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B3" t="n" s="0">
+        <v>50000.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>3.0468886E9</v>
+      </c>
+      <c r="D3" t="n" s="0">
+        <v>2.9635027E9</v>
+      </c>
+      <c r="E3" t="n" s="0">
+        <v>2.7190089E9</v>
+      </c>
+      <c r="F3" t="n" s="0">
+        <v>2.6799828E9</v>
+      </c>
+      <c r="G3" t="n" s="0">
+        <v>2.6907155E9</v>
+      </c>
+      <c r="H3" t="n" s="0">
+        <v>2.6898556E9</v>
+      </c>
+      <c r="I3" t="n" s="0">
+        <v>2.6788381E9</v>
+      </c>
+      <c r="J3" t="n" s="0">
+        <v>2.6851234E9</v>
+      </c>
+      <c r="K3" t="n" s="0">
+        <v>2.6620717E9</v>
+      </c>
+      <c r="L3" t="n" s="0">
+        <v>2.6686921E9</v>
+      </c>
+      <c r="M3" t="n" s="0">
+        <v>2.6724544E9</v>
+      </c>
+      <c r="N3" t="n" s="0">
+        <v>2.6627241E9</v>
+      </c>
+      <c r="O3" t="n" s="0">
+        <v>2.6614867E9</v>
+      </c>
+      <c r="P3" t="n" s="0">
+        <v>2.6841989E9</v>
+      </c>
+      <c r="Q3" t="n" s="0">
+        <v>2.69225E9</v>
+      </c>
+      <c r="R3" t="n" s="0">
+        <v>2.6757564E9</v>
+      </c>
+      <c r="S3" t="n" s="0">
+        <v>2.6452444E9</v>
+      </c>
+      <c r="T3" t="n" s="0">
+        <v>2.7035857E9</v>
+      </c>
+      <c r="U3" t="n" s="0">
+        <v>2.7033241E9</v>
+      </c>
+      <c r="V3" t="n" s="0">
+        <v>2.6548336E9</v>
+      </c>
+      <c r="W3" t="n" s="0">
+        <v>2.675122E9</v>
+      </c>
+      <c r="X3" t="n" s="0">
+        <v>2.6593563E9</v>
+      </c>
+      <c r="Y3" t="n" s="0">
+        <v>2.6575807E9</v>
+      </c>
+      <c r="Z3" t="n" s="0">
+        <v>2.6657774E9</v>
+      </c>
+      <c r="AA3" t="n" s="0">
+        <v>2.6867557E9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="B4" t="n" s="0">
+        <v>50000.0</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>3.230144E8</v>
+      </c>
+      <c r="D4" t="n" s="0">
+        <v>3.101351E8</v>
+      </c>
+      <c r="E4" t="n" s="0">
+        <v>3.168856E8</v>
+      </c>
+      <c r="F4" t="n" s="0">
+        <v>1.054946E8</v>
+      </c>
+      <c r="G4" t="n" s="0">
+        <v>9.39823E7</v>
+      </c>
+      <c r="H4" t="n" s="0">
+        <v>9.38593E7</v>
+      </c>
+      <c r="I4" t="n" s="0">
+        <v>9.2934E7</v>
+      </c>
+      <c r="J4" t="n" s="0">
+        <v>9.44079E7</v>
+      </c>
+      <c r="K4" t="n" s="0">
+        <v>9.28047E7</v>
+      </c>
+      <c r="L4" t="n" s="0">
+        <v>9.43885E7</v>
+      </c>
+      <c r="M4" t="n" s="0">
+        <v>9.4801E7</v>
+      </c>
+      <c r="N4" t="n" s="0">
+        <v>9.43986E7</v>
+      </c>
+      <c r="O4" t="n" s="0">
+        <v>9.59082E7</v>
+      </c>
+      <c r="P4" t="n" s="0">
+        <v>9.45419E7</v>
+      </c>
+      <c r="Q4" t="n" s="0">
+        <v>9.58958E7</v>
+      </c>
+      <c r="R4" t="n" s="0">
+        <v>9.85418E7</v>
+      </c>
+      <c r="S4" t="n" s="0">
+        <v>9.42742E7</v>
+      </c>
+      <c r="T4" t="n" s="0">
+        <v>9.65592E7</v>
+      </c>
+      <c r="U4" t="n" s="0">
+        <v>9.4327E7</v>
+      </c>
+      <c r="V4" t="n" s="0">
+        <v>9.41946E7</v>
+      </c>
+      <c r="W4" t="n" s="0">
+        <v>9.10291E7</v>
+      </c>
+      <c r="X4" t="n" s="0">
+        <v>9.45632E7</v>
+      </c>
+      <c r="Y4" t="n" s="0">
+        <v>9.587E7</v>
+      </c>
+      <c r="Z4" t="n" s="0">
+        <v>9.402E7</v>
+      </c>
+      <c r="AA4" t="n" s="0">
+        <v>9.57826E7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B5" t="n" s="0">
+        <v>50000.0</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>3.302582E8</v>
+      </c>
+      <c r="D5" t="n" s="0">
+        <v>3.201382E8</v>
+      </c>
+      <c r="E5" t="n" s="0">
+        <v>3.2855E8</v>
+      </c>
+      <c r="F5" t="n" s="0">
+        <v>9.3728E7</v>
+      </c>
+      <c r="G5" t="n" s="0">
+        <v>9.53895E7</v>
+      </c>
+      <c r="H5" t="n" s="0">
+        <v>9.50953E7</v>
+      </c>
+      <c r="I5" t="n" s="0">
+        <v>9.65851E7</v>
+      </c>
+      <c r="J5" t="n" s="0">
+        <v>9.84168E7</v>
+      </c>
+      <c r="K5" t="n" s="0">
+        <v>9.22568E7</v>
+      </c>
+      <c r="L5" t="n" s="0">
+        <v>9.47395E7</v>
+      </c>
+      <c r="M5" t="n" s="0">
+        <v>9.45283E7</v>
+      </c>
+      <c r="N5" t="n" s="0">
+        <v>9.4144E7</v>
+      </c>
+      <c r="O5" t="n" s="0">
+        <v>9.53502E7</v>
+      </c>
+      <c r="P5" t="n" s="0">
+        <v>9.64723E7</v>
+      </c>
+      <c r="Q5" t="n" s="0">
+        <v>9.42419E7</v>
+      </c>
+      <c r="R5" t="n" s="0">
+        <v>9.43755E7</v>
+      </c>
+      <c r="S5" t="n" s="0">
+        <v>1.006868E8</v>
+      </c>
+      <c r="T5" t="n" s="0">
+        <v>9.53014E7</v>
+      </c>
+      <c r="U5" t="n" s="0">
+        <v>9.40165E7</v>
+      </c>
+      <c r="V5" t="n" s="0">
+        <v>9.34873E7</v>
+      </c>
+      <c r="W5" t="n" s="0">
+        <v>9.03037E7</v>
+      </c>
+      <c r="X5" t="n" s="0">
+        <v>9.42095E7</v>
+      </c>
+      <c r="Y5" t="n" s="0">
+        <v>9.33692E7</v>
+      </c>
+      <c r="Z5" t="n" s="0">
+        <v>9.42064E7</v>
+      </c>
+      <c r="AA5" t="n" s="0">
+        <v>9.57864E7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n" s="0">
+        <v>50000.0</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>5.827125E8</v>
+      </c>
+      <c r="D6" t="n" s="0">
+        <v>5.788229E8</v>
+      </c>
+      <c r="E6" t="n" s="0">
+        <v>3.325924E8</v>
+      </c>
+      <c r="F6" t="n" s="0">
+        <v>3.268567E8</v>
+      </c>
+      <c r="G6" t="n" s="0">
+        <v>3.276992E8</v>
+      </c>
+      <c r="H6" t="n" s="0">
+        <v>3.286945E8</v>
+      </c>
+      <c r="I6" t="n" s="0">
+        <v>3.34382E8</v>
+      </c>
+      <c r="J6" t="n" s="0">
+        <v>3.306941E8</v>
+      </c>
+      <c r="K6" t="n" s="0">
+        <v>3.290219E8</v>
+      </c>
+      <c r="L6" t="n" s="0">
+        <v>3.264315E8</v>
+      </c>
+      <c r="M6" t="n" s="0">
+        <v>3.298752E8</v>
+      </c>
+      <c r="N6" t="n" s="0">
+        <v>3.340853E8</v>
+      </c>
+      <c r="O6" t="n" s="0">
+        <v>3.287008E8</v>
+      </c>
+      <c r="P6" t="n" s="0">
+        <v>3.296775E8</v>
+      </c>
+      <c r="Q6" t="n" s="0">
+        <v>3.261659E8</v>
+      </c>
+      <c r="R6" t="n" s="0">
+        <v>3.296493E8</v>
+      </c>
+      <c r="S6" t="n" s="0">
+        <v>3.309483E8</v>
+      </c>
+      <c r="T6" t="n" s="0">
+        <v>3.265969E8</v>
+      </c>
+      <c r="U6" t="n" s="0">
+        <v>3.252038E8</v>
+      </c>
+      <c r="V6" t="n" s="0">
+        <v>3.418137E8</v>
+      </c>
+      <c r="W6" t="n" s="0">
+        <v>3.315679E8</v>
+      </c>
+      <c r="X6" t="n" s="0">
+        <v>3.277795E8</v>
+      </c>
+      <c r="Y6" t="n" s="0">
+        <v>3.26809E8</v>
+      </c>
+      <c r="Z6" t="n" s="0">
+        <v>3.26038E8</v>
+      </c>
+      <c r="AA6" t="n" s="0">
+        <v>3.303419E8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B7" t="n" s="0">
+        <v>50000.0</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>6.522282E8</v>
+      </c>
+      <c r="D7" t="n" s="0">
+        <v>5.818467E8</v>
+      </c>
+      <c r="E7" t="n" s="0">
+        <v>3.329693E8</v>
+      </c>
+      <c r="F7" t="n" s="0">
+        <v>3.282731E8</v>
+      </c>
+      <c r="G7" t="n" s="0">
+        <v>3.25403E8</v>
+      </c>
+      <c r="H7" t="n" s="0">
+        <v>3.300484E8</v>
+      </c>
+      <c r="I7" t="n" s="0">
+        <v>3.289061E8</v>
+      </c>
+      <c r="J7" t="n" s="0">
+        <v>3.270118E8</v>
+      </c>
+      <c r="K7" t="n" s="0">
+        <v>3.28864E8</v>
+      </c>
+      <c r="L7" t="n" s="0">
+        <v>3.264421E8</v>
+      </c>
+      <c r="M7" t="n" s="0">
+        <v>3.279674E8</v>
+      </c>
+      <c r="N7" t="n" s="0">
+        <v>3.291429E8</v>
+      </c>
+      <c r="O7" t="n" s="0">
+        <v>3.268561E8</v>
+      </c>
+      <c r="P7" t="n" s="0">
+        <v>3.299827E8</v>
+      </c>
+      <c r="Q7" t="n" s="0">
+        <v>3.290533E8</v>
+      </c>
+      <c r="R7" t="n" s="0">
+        <v>3.260025E8</v>
+      </c>
+      <c r="S7" t="n" s="0">
+        <v>3.313146E8</v>
+      </c>
+      <c r="T7" t="n" s="0">
+        <v>3.3037E8</v>
+      </c>
+      <c r="U7" t="n" s="0">
+        <v>3.257834E8</v>
+      </c>
+      <c r="V7" t="n" s="0">
+        <v>3.263011E8</v>
+      </c>
+      <c r="W7" t="n" s="0">
+        <v>3.461623E8</v>
+      </c>
+      <c r="X7" t="n" s="0">
+        <v>3.273283E8</v>
+      </c>
+      <c r="Y7" t="n" s="0">
+        <v>3.412981E8</v>
+      </c>
+      <c r="Z7" t="n" s="0">
+        <v>3.248854E8</v>
+      </c>
+      <c r="AA7" t="n" s="0">
+        <v>3.270838E8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B8" t="n" s="0">
+        <v>50000.0</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>1.46127E7</v>
+      </c>
+      <c r="D8" t="n" s="0">
+        <v>4682400.0</v>
+      </c>
+      <c r="E8" t="n" s="0">
+        <v>4406400.0</v>
+      </c>
+      <c r="F8" t="n" s="0">
+        <v>3.64927E7</v>
+      </c>
+      <c r="G8" t="n" s="0">
+        <v>4.31753E7</v>
+      </c>
+      <c r="H8" t="n" s="0">
+        <v>5342000.0</v>
+      </c>
+      <c r="I8" t="n" s="0">
+        <v>3.55544E7</v>
+      </c>
+      <c r="J8" t="n" s="0">
+        <v>5381700.0</v>
+      </c>
+      <c r="K8" t="n" s="0">
+        <v>5371000.0</v>
+      </c>
+      <c r="L8" t="n" s="0">
+        <v>4481600.0</v>
+      </c>
+      <c r="M8" t="n" s="0">
+        <v>5266000.0</v>
+      </c>
+      <c r="N8" t="n" s="0">
+        <v>5788800.0</v>
+      </c>
+      <c r="O8" t="n" s="0">
+        <v>4764400.0</v>
+      </c>
+      <c r="P8" t="n" s="0">
+        <v>4667200.0</v>
+      </c>
+      <c r="Q8" t="n" s="0">
+        <v>5726900.0</v>
+      </c>
+      <c r="R8" t="n" s="0">
+        <v>6251400.0</v>
+      </c>
+      <c r="S8" t="n" s="0">
+        <v>5853500.0</v>
+      </c>
+      <c r="T8" t="n" s="0">
+        <v>4293400.0</v>
+      </c>
+      <c r="U8" t="n" s="0">
+        <v>5782700.0</v>
+      </c>
+      <c r="V8" t="n" s="0">
+        <v>5655200.0</v>
+      </c>
+      <c r="W8" t="n" s="0">
+        <v>4734400.0</v>
+      </c>
+      <c r="X8" t="n" s="0">
+        <v>5599800.0</v>
+      </c>
+      <c r="Y8" t="n" s="0">
+        <v>4635300.0</v>
+      </c>
+      <c r="Z8" t="n" s="0">
+        <v>4371300.0</v>
+      </c>
+      <c r="AA8" t="n" s="0">
+        <v>5625100.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B9" t="n" s="0">
+        <v>50000.0</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>1.83766E7</v>
+      </c>
+      <c r="D9" t="n" s="0">
+        <v>4333700.0</v>
+      </c>
+      <c r="E9" t="n" s="0">
+        <v>4589300.0</v>
+      </c>
+      <c r="F9" t="n" s="0">
+        <v>4756900.0</v>
+      </c>
+      <c r="G9" t="n" s="0">
+        <v>5082600.0</v>
+      </c>
+      <c r="H9" t="n" s="0">
+        <v>5273300.0</v>
+      </c>
+      <c r="I9" t="n" s="0">
+        <v>4496600.0</v>
+      </c>
+      <c r="J9" t="n" s="0">
+        <v>5269300.0</v>
+      </c>
+      <c r="K9" t="n" s="0">
+        <v>5172800.0</v>
+      </c>
+      <c r="L9" t="n" s="0">
+        <v>4379900.0</v>
+      </c>
+      <c r="M9" t="n" s="0">
+        <v>5854000.0</v>
+      </c>
+      <c r="N9" t="n" s="0">
+        <v>6256200.0</v>
+      </c>
+      <c r="O9" t="n" s="0">
+        <v>4430400.0</v>
+      </c>
+      <c r="P9" t="n" s="0">
+        <v>4.76892E7</v>
+      </c>
+      <c r="Q9" t="n" s="0">
+        <v>6229500.0</v>
+      </c>
+      <c r="R9" t="n" s="0">
+        <v>6121200.0</v>
+      </c>
+      <c r="S9" t="n" s="0">
+        <v>6264600.0</v>
+      </c>
+      <c r="T9" t="n" s="0">
+        <v>4315500.0</v>
+      </c>
+      <c r="U9" t="n" s="0">
+        <v>5904500.0</v>
+      </c>
+      <c r="V9" t="n" s="0">
+        <v>6019100.0</v>
+      </c>
+      <c r="W9" t="n" s="0">
+        <v>4797200.0</v>
+      </c>
+      <c r="X9" t="n" s="0">
+        <v>5963000.0</v>
+      </c>
+      <c r="Y9" t="n" s="0">
+        <v>4320300.0</v>
+      </c>
+      <c r="Z9" t="n" s="0">
+        <v>4256300.0</v>
+      </c>
+      <c r="AA9" t="n" s="0">
+        <v>6352100.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B10" t="n" s="0">
+        <v>50000.0</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>1.22773E7</v>
+      </c>
+      <c r="D10" t="n" s="0">
+        <v>4851600.0</v>
+      </c>
+      <c r="E10" t="n" s="0">
+        <v>4882800.0</v>
+      </c>
+      <c r="F10" t="n" s="0">
+        <v>6444300.0</v>
+      </c>
+      <c r="G10" t="n" s="0">
+        <v>5849000.0</v>
+      </c>
+      <c r="H10" t="n" s="0">
+        <v>6700700.0</v>
+      </c>
+      <c r="I10" t="n" s="0">
+        <v>4836800.0</v>
+      </c>
+      <c r="J10" t="n" s="0">
+        <v>6540900.0</v>
+      </c>
+      <c r="K10" t="n" s="0">
+        <v>6517700.0</v>
+      </c>
+      <c r="L10" t="n" s="0">
+        <v>4896400.0</v>
+      </c>
+      <c r="M10" t="n" s="0">
+        <v>7819900.0</v>
+      </c>
+      <c r="N10" t="n" s="0">
+        <v>5.67063E7</v>
+      </c>
+      <c r="O10" t="n" s="0">
+        <v>4931700.0</v>
+      </c>
+      <c r="P10" t="n" s="0">
+        <v>5213300.0</v>
+      </c>
+      <c r="Q10" t="n" s="0">
+        <v>7575500.0</v>
+      </c>
+      <c r="R10" t="n" s="0">
+        <v>8284600.0</v>
+      </c>
+      <c r="S10" t="n" s="0">
+        <v>7496100.0</v>
+      </c>
+      <c r="T10" t="n" s="0">
+        <v>4747200.0</v>
+      </c>
+      <c r="U10" t="n" s="0">
+        <v>7271100.0</v>
+      </c>
+      <c r="V10" t="n" s="0">
+        <v>7494800.0</v>
+      </c>
+      <c r="W10" t="n" s="0">
+        <v>5105800.0</v>
+      </c>
+      <c r="X10" t="n" s="0">
+        <v>7593600.0</v>
+      </c>
+      <c r="Y10" t="n" s="0">
+        <v>4838300.0</v>
+      </c>
+      <c r="Z10" t="n" s="0">
+        <v>5182400.0</v>
+      </c>
+      <c r="AA10" t="n" s="0">
+        <v>7586400.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B11" t="n" s="0">
+        <v>50000.0</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>1.06816E7</v>
+      </c>
+      <c r="D11" t="n" s="0">
+        <v>7228200.0</v>
+      </c>
+      <c r="E11" t="n" s="0">
+        <v>4949500.0</v>
+      </c>
+      <c r="F11" t="n" s="0">
+        <v>6780600.0</v>
+      </c>
+      <c r="G11" t="n" s="0">
+        <v>5431400.0</v>
+      </c>
+      <c r="H11" t="n" s="0">
+        <v>6561200.0</v>
+      </c>
+      <c r="I11" t="n" s="0">
+        <v>4946500.0</v>
+      </c>
+      <c r="J11" t="n" s="0">
+        <v>1.77641E7</v>
+      </c>
+      <c r="K11" t="n" s="0">
+        <v>6600400.0</v>
+      </c>
+      <c r="L11" t="n" s="0">
+        <v>5.4383E7</v>
+      </c>
+      <c r="M11" t="n" s="0">
+        <v>8140000.0</v>
+      </c>
+      <c r="N11" t="n" s="0">
+        <v>5204800.0</v>
+      </c>
+      <c r="O11" t="n" s="0">
+        <v>4.8703E7</v>
+      </c>
+      <c r="P11" t="n" s="0">
+        <v>5374100.0</v>
+      </c>
+      <c r="Q11" t="n" s="0">
+        <v>7860100.0</v>
+      </c>
+      <c r="R11" t="n" s="0">
+        <v>7916900.0</v>
+      </c>
+      <c r="S11" t="n" s="0">
+        <v>7947100.0</v>
+      </c>
+      <c r="T11" t="n" s="0">
+        <v>4782700.0</v>
+      </c>
+      <c r="U11" t="n" s="0">
+        <v>7903400.0</v>
+      </c>
+      <c r="V11" t="n" s="0">
+        <v>7.40772E7</v>
+      </c>
+      <c r="W11" t="n" s="0">
+        <v>5218900.0</v>
+      </c>
+      <c r="X11" t="n" s="0">
+        <v>8267900.0</v>
+      </c>
+      <c r="Y11" t="n" s="0">
+        <v>4908500.0</v>
+      </c>
+      <c r="Z11" t="n" s="0">
+        <v>4960500.0</v>
+      </c>
+      <c r="AA11" t="n" s="0">
+        <v>7998400.0</v>
       </c>
     </row>
   </sheetData>
